--- a/templates/supervisory-capacity-records.xlsx
+++ b/templates/supervisory-capacity-records.xlsx
@@ -1667,7 +1667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="22" min="1" max="1"/>
@@ -1843,35 +1843,52 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="28.5" customHeight="1" s="22">
+    <row r="13" ht="15" customHeight="1" s="22">
       <c r="A13" s="62" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Registered condition to decline</t>
         </is>
       </c>
       <c r="B13" s="63" t="inlineStr">
         <is>
-          <t>Declared, and published in full including the limits above</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="C13" s="64" t="inlineStr">
         <is>
-          <t>Not a verdict on the people. A statement of what the work reached.</t>
+          <t>The condition under which the function would decline to conclude, fixed before the work. Naming it in advance is cheap; deciding it afterwards is the failure mode.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28.5" customHeight="1" s="22">
       <c r="A14" s="62" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>Declared, and published in full including the limits above</t>
+        </is>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>Not a verdict on the people. A statement of what the work reached.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
           <t>What it does not support</t>
         </is>
       </c>
-      <c r="B14" s="63" t="inlineStr">
+      <c r="B15" s="63" t="inlineStr">
         <is>
           <t>Any claim that behaviour of this kind would be caught next time under the same conditions</t>
         </is>
       </c>
-      <c r="C14" s="64" t="inlineStr">
+      <c r="C15" s="64" t="inlineStr">
         <is>
           <t>The sentence a reader would otherwise supply for themselves, wrongly.</t>
         </is>
@@ -2635,7 +2652,7 @@
       </c>
       <c r="U1" s="48" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>record_status</t>
         </is>
       </c>
     </row>
